--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/08,09,26 Останкино Сыры/дв 08,09,26 млрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/08,09,26 Останкино Сыры/дв 08,09,26 млрсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\08,09,26 Останкино Сыры\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A600DC4-262C-4582-A65B-0FF72809466F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26063EE6-A880-4FEC-AF37-5FBFE38662B2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -143,9 +143,6 @@
   </si>
   <si>
     <t>шт</t>
-  </si>
-  <si>
-    <t>03,09,26 - нет на заводе / 30,07,26 - нет на заводе</t>
   </si>
   <si>
     <t>4421584 Спред растительно-сливочный "Сливочный вкус" 72,5% 180гр  Останкино</t>
@@ -326,6 +323,9 @@
   <si>
     <t>заказ</t>
   </si>
+  <si>
+    <t>10,09,26 - нет на заводе / 03,09,26 - нет на заводе / 30,07,26 - нет на заводе</t>
+  </si>
 </sst>
 </file>
 
@@ -377,7 +377,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -409,6 +409,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -448,7 +454,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -466,6 +472,7 @@
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -942,10 +949,10 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="R3" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>16</v>
@@ -1131,7 +1138,7 @@
       </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -1278,7 +1285,7 @@
         <v>10.6188</v>
       </c>
       <c r="AE6" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AF6" s="1">
         <f t="shared" ref="AF6:AF46" si="6">G6*Q6</f>
@@ -1342,9 +1349,8 @@
       <c r="Q7" s="5">
         <v>12</v>
       </c>
-      <c r="R7" s="5">
-        <f>VLOOKUP(A7,заказ!A:B,2,0)</f>
-        <v>12</v>
+      <c r="R7" s="17">
+        <v>0</v>
       </c>
       <c r="S7" s="1" t="e">
         <f t="shared" si="4"/>
@@ -1385,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="AF7" s="1">
         <f t="shared" si="6"/>
@@ -1411,7 +1417,7 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>36</v>
@@ -1453,9 +1459,8 @@
       <c r="Q8" s="5">
         <v>12</v>
       </c>
-      <c r="R8" s="5">
-        <f>VLOOKUP(A8,заказ!A:B,2,0)</f>
-        <v>12</v>
+      <c r="R8" s="17">
+        <v>0</v>
       </c>
       <c r="S8" s="1">
         <f t="shared" si="4"/>
@@ -1496,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="AF8" s="1">
         <f t="shared" si="6"/>
@@ -1522,7 +1527,7 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>34</v>
@@ -1602,7 +1607,7 @@
         <v>3.8519999999999999</v>
       </c>
       <c r="AE9" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF9" s="1">
         <f t="shared" si="6"/>
@@ -1628,7 +1633,7 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>36</v>
@@ -1702,7 +1707,7 @@
         <v>4.8</v>
       </c>
       <c r="AE10" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF10" s="1">
         <f t="shared" si="6"/>
@@ -1728,7 +1733,7 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>36</v>
@@ -1806,7 +1811,7 @@
         <v>49</v>
       </c>
       <c r="AE11" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF11" s="1">
         <f t="shared" si="6"/>
@@ -1832,7 +1837,7 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>36</v>
@@ -1910,7 +1915,7 @@
         <v>40.6</v>
       </c>
       <c r="AE12" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF12" s="1">
         <f t="shared" si="6"/>
@@ -1936,7 +1941,7 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>36</v>
@@ -2040,7 +2045,7 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>36</v>
@@ -2144,7 +2149,7 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>36</v>
@@ -2222,7 +2227,7 @@
         <v>15.2</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF15" s="1">
         <f t="shared" si="6"/>
@@ -2248,7 +2253,7 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>36</v>
@@ -2360,7 +2365,7 @@
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>36</v>
@@ -2472,7 +2477,7 @@
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>36</v>
@@ -2548,7 +2553,7 @@
         <v>6</v>
       </c>
       <c r="AE18" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF18" s="1">
         <f t="shared" si="6"/>
@@ -2574,7 +2579,7 @@
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>36</v>
@@ -2680,7 +2685,7 @@
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>36</v>
@@ -2786,7 +2791,7 @@
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>36</v>
@@ -2892,7 +2897,7 @@
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>36</v>
@@ -2972,7 +2977,7 @@
         <v>0.2</v>
       </c>
       <c r="AE22" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AF22" s="1">
         <f t="shared" si="6"/>
@@ -2998,7 +3003,7 @@
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>36</v>
@@ -3108,7 +3113,7 @@
     </row>
     <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>36</v>
@@ -3210,7 +3215,7 @@
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>36</v>
@@ -3288,7 +3293,7 @@
         <v>0.6</v>
       </c>
       <c r="AE25" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF25" s="1">
         <f t="shared" si="6"/>
@@ -3314,7 +3319,7 @@
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>34</v>
@@ -3388,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="AE26" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF26" s="1">
         <f t="shared" si="6"/>
@@ -3414,7 +3419,7 @@
     </row>
     <row r="27" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>34</v>
@@ -3488,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="AE27" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AF27" s="1">
         <f t="shared" si="6"/>
@@ -3514,7 +3519,7 @@
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>36</v>
@@ -3596,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="AE28" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AF28" s="1">
         <f t="shared" si="6"/>
@@ -3622,7 +3627,7 @@
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>36</v>
@@ -3702,7 +3707,7 @@
         <v>3.8</v>
       </c>
       <c r="AE29" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AF29" s="1">
         <f t="shared" si="6"/>
@@ -3728,7 +3733,7 @@
     </row>
     <row r="30" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>36</v>
@@ -3830,7 +3835,7 @@
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>36</v>
@@ -3908,7 +3913,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="AE31" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF31" s="1">
         <f t="shared" si="6"/>
@@ -3934,7 +3939,7 @@
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>36</v>
@@ -4014,7 +4019,7 @@
         <v>52.8</v>
       </c>
       <c r="AE32" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF32" s="1">
         <f t="shared" si="6"/>
@@ -4040,7 +4045,7 @@
     </row>
     <row r="33" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>36</v>
@@ -4120,7 +4125,7 @@
         <v>60.2</v>
       </c>
       <c r="AE33" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF33" s="1">
         <f t="shared" si="6"/>
@@ -4146,7 +4151,7 @@
     </row>
     <row r="34" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>36</v>
@@ -4226,7 +4231,7 @@
         <v>26</v>
       </c>
       <c r="AE34" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF34" s="1">
         <f t="shared" si="6"/>
@@ -4252,7 +4257,7 @@
     </row>
     <row r="35" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>36</v>
@@ -4334,7 +4339,7 @@
         <v>33.799999999999997</v>
       </c>
       <c r="AE35" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AF35" s="1">
         <f t="shared" si="6"/>
@@ -4360,7 +4365,7 @@
     </row>
     <row r="36" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>36</v>
@@ -4442,7 +4447,7 @@
         <v>68.599999999999994</v>
       </c>
       <c r="AE36" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AF36" s="1">
         <f t="shared" si="6"/>
@@ -4468,7 +4473,7 @@
     </row>
     <row r="37" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>36</v>
@@ -4550,7 +4555,7 @@
         <v>29</v>
       </c>
       <c r="AE37" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AF37" s="1">
         <f t="shared" si="6"/>
@@ -4576,7 +4581,7 @@
     </row>
     <row r="38" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>36</v>
@@ -4686,7 +4691,7 @@
     </row>
     <row r="39" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>36</v>
@@ -4764,7 +4769,7 @@
         <v>31.6</v>
       </c>
       <c r="AE39" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF39" s="1">
         <f t="shared" si="6"/>
@@ -4790,7 +4795,7 @@
     </row>
     <row r="40" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>34</v>
@@ -4868,7 +4873,7 @@
         <v>5.4383999999999997</v>
       </c>
       <c r="AE40" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF40" s="1">
         <f t="shared" si="6"/>
@@ -4894,7 +4899,7 @@
     </row>
     <row r="41" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>34</v>
@@ -4972,7 +4977,7 @@
         <v>4.0278</v>
       </c>
       <c r="AE41" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF41" s="1">
         <f t="shared" si="6"/>
@@ -4998,7 +5003,7 @@
     </row>
     <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>34</v>
@@ -5076,7 +5081,7 @@
         <v>9.7864000000000004</v>
       </c>
       <c r="AE42" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AF42" s="1">
         <f t="shared" si="6"/>
@@ -5102,7 +5107,7 @@
     </row>
     <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>34</v>
@@ -5180,7 +5185,7 @@
         <v>1.9708000000000001</v>
       </c>
       <c r="AE43" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF43" s="1">
         <f t="shared" si="6"/>
@@ -5206,7 +5211,7 @@
     </row>
     <row r="44" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>36</v>
@@ -5284,7 +5289,7 @@
         <v>6.8</v>
       </c>
       <c r="AE44" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AF44" s="1">
         <f t="shared" si="6"/>
@@ -5310,7 +5315,7 @@
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>36</v>
@@ -5388,7 +5393,7 @@
         <v>15.2</v>
       </c>
       <c r="AE45" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AF45" s="1">
         <f t="shared" si="6"/>
@@ -5414,7 +5419,7 @@
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>36</v>
@@ -5524,7 +5529,7 @@
     </row>
     <row r="47" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>36</v>
@@ -5546,10 +5551,10 @@
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="J47" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>82</v>
       </c>
       <c r="K47" s="9">
         <v>88</v>
@@ -5627,7 +5632,7 @@
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>36</v>
@@ -5735,7 +5740,7 @@
     </row>
     <row r="49" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>34</v>
@@ -5811,7 +5816,7 @@
         <v>0</v>
       </c>
       <c r="AE49" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF49" s="1">
         <f>G49*Q49</f>
@@ -5837,7 +5842,7 @@
     </row>
     <row r="50" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>36</v>
@@ -5857,10 +5862,10 @@
       </c>
       <c r="H50" s="9"/>
       <c r="I50" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K50" s="9">
         <v>87</v>
@@ -5938,7 +5943,7 @@
     </row>
     <row r="51" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>36</v>
@@ -6048,7 +6053,7 @@
     </row>
     <row r="52" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>34</v>
@@ -6128,7 +6133,7 @@
         <v>24.588799999999999</v>
       </c>
       <c r="AE52" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF52" s="1">
         <f>G52*Q52</f>
@@ -6154,7 +6159,7 @@
     </row>
     <row r="53" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>34</v>
@@ -6172,10 +6177,10 @@
       </c>
       <c r="H53" s="9"/>
       <c r="I53" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K53" s="9">
         <v>30</v>
@@ -29070,7 +29075,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -29078,7 +29083,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3">
         <v>80</v>
@@ -29086,7 +29091,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B4">
         <v>96</v>
@@ -29094,7 +29099,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5">
         <v>28</v>
@@ -29102,7 +29107,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B6">
         <v>16</v>
@@ -29110,7 +29115,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B7">
         <v>48</v>
@@ -29118,7 +29123,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8">
         <v>50</v>
@@ -29126,7 +29131,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B9">
         <v>80</v>
